--- a/data/DataSet31/FitRNet_Storage_RawData.xlsx
+++ b/data/DataSet31/FitRNet_Storage_RawData.xlsx
@@ -1,21 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/43e2b3cea5fa3503/Documents/Thesis Stuff/abs-normal/data/DataSet31/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_514DD4178AE69C8781C3E5F9D6C107C8118A06DD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4EC81AB0-121A-4F3C-AF7B-6FB3D202249E}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="12288" windowHeight="8268" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="125725" fullCalcOnLoad="true"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -29,7 +49,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -37,1944 +57,2267 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D100"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.5546875" customWidth="true"/>
-    <col min="2" max="2" width="15.5546875" customWidth="true"/>
-    <col min="3" max="3" width="12.5546875" customWidth="true"/>
-    <col min="4" max="4" width="12.5546875" customWidth="true"/>
+    <col min="1" max="2" width="15.5546875" customWidth="1"/>
+    <col min="3" max="4" width="12.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="0">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1">
         <v>4</v>
       </c>
-      <c r="B1" s="0">
+      <c r="B1">
         <v>1</v>
       </c>
-      <c r="C1" s="0">
+      <c r="C1">
         <v>0.5</v>
       </c>
-      <c r="D1" s="0">
+      <c r="D1">
         <v>0</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="0">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2">
         <v>3.5649243538909339</v>
       </c>
-      <c r="B2" s="0">
+      <c r="B2">
         <v>1.3216021732177254</v>
       </c>
-      <c r="C2" s="0">
+      <c r="C2">
         <v>0.64400509717969623</v>
       </c>
-      <c r="D2" s="0">
+      <c r="D2">
         <v>0.57908074328876247</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="0">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>3.1771559183256364</v>
       </c>
-      <c r="B3" s="0">
+      <c r="B3">
         <v>1.5584188674899142</v>
       </c>
-      <c r="C3" s="0">
+      <c r="C3">
         <v>0.82216865851247523</v>
       </c>
-      <c r="D3" s="0">
+      <c r="D3">
         <v>1.1450127401868391</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="0">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>2.8315559725453188</v>
       </c>
-      <c r="B4" s="0">
+      <c r="B4">
         <v>1.7254180201273206</v>
       </c>
-      <c r="C4" s="0">
-        <v>1.0250220794294434</v>
-      </c>
-      <c r="D4" s="0">
+      <c r="C4">
+        <v>1.0250220794294433</v>
+      </c>
+      <c r="D4">
         <v>1.6934661068841241</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="0">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5">
         <v>2.5235863043954296</v>
       </c>
-      <c r="B5" s="0">
+      <c r="B5">
         <v>1.8350112615070389</v>
       </c>
-      <c r="C5" s="0">
+      <c r="C5">
         <v>1.2450104127364483</v>
       </c>
-      <c r="D5" s="0">
+      <c r="D5">
         <v>2.2214241083410187</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="0">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6">
         <v>2.2491225550100271</v>
       </c>
-      <c r="B6" s="0">
+      <c r="B6">
         <v>1.8981521709640439</v>
       </c>
-      <c r="C6" s="0">
+      <c r="C6">
         <v>1.475593866656804</v>
       </c>
-      <c r="D6" s="0">
+      <c r="D6">
         <v>2.7264713116467769</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="0">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7">
         <v>2.0044583933803293</v>
       </c>
-      <c r="B7" s="0">
+      <c r="B7">
         <v>1.9242596864683101</v>
       </c>
-      <c r="C7" s="0">
+      <c r="C7">
         <v>1.7113199276334423</v>
       </c>
-      <c r="D7" s="0">
+      <c r="D7">
         <v>3.2068615342531124</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="0">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8">
         <v>1.7864062889105807</v>
       </c>
-      <c r="B8" s="0">
+      <c r="B8">
         <v>1.9205826369174708</v>
       </c>
-      <c r="C8" s="0">
+      <c r="C8">
         <v>1.9483509837220832</v>
       </c>
-      <c r="D8" s="0">
+      <c r="D8">
         <v>3.6619446948115018</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="0">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9">
         <v>1.5921169452087582</v>
       </c>
-      <c r="B9" s="0">
+      <c r="B9">
         <v>1.8932312615458273</v>
       </c>
-      <c r="C9" s="0">
+      <c r="C9">
         <v>2.1836260427044483</v>
       </c>
-      <c r="D9" s="0">
+      <c r="D9">
         <v>4.09150909749569</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="0">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10">
         <v>1.4189810428049747</v>
       </c>
-      <c r="B10" s="0">
+      <c r="B10">
         <v>1.8476737045441449</v>
       </c>
-      <c r="C10" s="0">
+      <c r="C10">
         <v>2.4144693899978997</v>
       </c>
-      <c r="D10" s="0">
+      <c r="D10">
         <v>4.4954883471929241</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="0">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11">
         <v>1.2646328963956772</v>
       </c>
-      <c r="B11" s="0">
+      <c r="B11">
         <v>1.7886951990857407</v>
       </c>
-      <c r="C11" s="0">
+      <c r="C11">
         <v>2.6386274907364289</v>
       </c>
-      <c r="D11" s="0">
+      <c r="D11">
         <v>4.8739945943407514</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="0">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12">
         <v>1.127039739454355</v>
       </c>
-      <c r="B12" s="0">
+      <c r="B12">
         <v>1.7198391375513686</v>
       </c>
-      <c r="C12" s="0">
+      <c r="C12">
         <v>2.8547323693483566</v>
       </c>
-      <c r="D12" s="0">
+      <c r="D12">
         <v>5.2276926298940012</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="0">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13">
         <v>1.0044418893652149</v>
       </c>
-      <c r="B13" s="0">
-        <v>1.6437800775970029</v>
-      </c>
-      <c r="C13" s="0">
+      <c r="B13">
+        <v>1.6437800775970028</v>
+      </c>
+      <c r="C13">
         <v>3.0619926372928545</v>
       </c>
-      <c r="D13" s="0">
+      <c r="D13">
         <v>5.5575507479276389</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="0">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14">
         <v>0.89521806937137238</v>
       </c>
-      <c r="B14" s="0">
+      <c r="B14">
         <v>1.5629348471435973</v>
       </c>
-      <c r="C14" s="0">
+      <c r="C14">
         <v>3.2597265172133545</v>
       </c>
-      <c r="D14" s="0">
+      <c r="D14">
         <v>5.864508447841982</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="0">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15">
         <v>0.79788007031715025</v>
       </c>
-      <c r="B15" s="0">
+      <c r="B15">
         <v>1.479479052842569</v>
       </c>
-      <c r="C15" s="0">
+      <c r="C15">
         <v>3.4473510473443398</v>
       </c>
-      <c r="D15" s="0">
+      <c r="D15">
         <v>6.1494709770271889</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="0">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16">
         <v>0.71108112757850794</v>
       </c>
-      <c r="B16" s="0">
+      <c r="B16">
         <v>1.3952776366020925</v>
       </c>
-      <c r="C16" s="0">
+      <c r="C16">
         <v>3.6244425601998547</v>
       </c>
-      <c r="D16" s="0">
+      <c r="D16">
         <v>6.4133614326213468</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="0">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17">
         <v>0.6336983218293879</v>
       </c>
-      <c r="B17" s="0">
+      <c r="B17">
         <v>1.3114510087388984</v>
       </c>
-      <c r="C17" s="0">
+      <c r="C17">
         <v>3.7910823661454405</v>
       </c>
-      <c r="D17" s="0">
+      <c r="D17">
         <v>6.6573840443160526</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="0">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18">
         <v>0.56475651569313712</v>
       </c>
-      <c r="B18" s="0">
+      <c r="B18">
         <v>1.2287856171258189</v>
       </c>
-      <c r="C18" s="0">
+      <c r="C18">
         <v>3.9475275853780163</v>
       </c>
-      <c r="D18" s="0">
+      <c r="D18">
         <v>6.8827710696848792</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="0">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19">
         <v>0.50334927348365743</v>
       </c>
-      <c r="B19" s="0">
+      <c r="B19">
         <v>1.1480131708591155</v>
       </c>
-      <c r="C19" s="0">
+      <c r="C19">
         <v>4.0940165540092508</v>
       </c>
-      <c r="D19" s="0">
+      <c r="D19">
         <v>7.0906672805255928</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="0">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20">
         <v>0.44863768027706341</v>
       </c>
-      <c r="B20" s="0">
+      <c r="B20">
         <v>1.0698115967840507</v>
       </c>
-      <c r="C20" s="0">
+      <c r="C20">
         <v>4.2307691313404954</v>
       </c>
-      <c r="D20" s="0">
+      <c r="D20">
         <v>7.2821314510634316</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="0">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21">
         <v>0.3998509317014049</v>
       </c>
-      <c r="B21" s="0">
+      <c r="B21">
         <v>0.99479904994424628</v>
       </c>
-      <c r="C21" s="0">
+      <c r="C21">
         <v>4.3579920582349514</v>
       </c>
-      <c r="D21" s="0">
+      <c r="D21">
         <v>7.4581411265335467</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="0">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22">
         <v>0.35633049827514851</v>
       </c>
-      <c r="B22" s="0">
+      <c r="B22">
         <v>0.92329330639322504</v>
       </c>
-      <c r="C22" s="0">
-        <v>4.4760723007158259</v>
-      </c>
-      <c r="D22" s="0">
+      <c r="C22">
+        <v>4.4760723007158258</v>
+      </c>
+      <c r="D22">
         <v>7.6197418024406778</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="0">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23">
         <v>0.3175446074761174</v>
       </c>
-      <c r="B23" s="0">
+      <c r="B23">
         <v>0.85531942778289394</v>
       </c>
-      <c r="C23" s="0">
+      <c r="C23">
         <v>4.5855538870233659</v>
       </c>
-      <c r="D23" s="0">
+      <c r="D23">
         <v>7.7680092795472486</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="0">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24">
         <v>0.28300171486319448</v>
       </c>
-      <c r="B24" s="0">
+      <c r="B24">
         <v>0.79090594221879196</v>
       </c>
-      <c r="C24" s="0">
+      <c r="C24">
         <v>4.6869343278398947</v>
       </c>
-      <c r="D24" s="0">
+      <c r="D24">
         <v>7.9039326129766998</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="0">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25">
         <v>0.2522418958181617</v>
       </c>
-      <c r="B25" s="0">
-        <v>0.73009191261265905</v>
-      </c>
-      <c r="C25" s="0">
+      <c r="B25">
+        <v>0.73009191261265904</v>
+      </c>
+      <c r="C25">
         <v>4.7806667602836939</v>
       </c>
-      <c r="D25" s="0">
+      <c r="D25">
         <v>8.0284248644655314</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="0">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26">
         <v>0.22483684554569972</v>
       </c>
-      <c r="B26" s="0">
+      <c r="B26">
         <v>0.67292693668243553</v>
       </c>
-      <c r="C26" s="0">
+      <c r="C26">
         <v>4.8671599479090082</v>
       </c>
-      <c r="D26" s="0">
+      <c r="D26">
         <v>8.1423231023633083</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="0">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27">
         <v>0.20039049717255555</v>
       </c>
-      <c r="B27" s="0">
+      <c r="B27">
         <v>0.61946644508413606</v>
       </c>
-      <c r="C27" s="0">
+      <c r="C27">
         <v>4.9467823210996196</v>
       </c>
-      <c r="D27" s="0">
+      <c r="D27">
         <v>8.2463918239270644</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="0">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28">
         <v>0.17857270250681681</v>
       </c>
-      <c r="B28" s="0">
+      <c r="B28">
         <v>0.56961663139893637</v>
       </c>
-      <c r="C28" s="0">
+      <c r="C28">
         <v>5.019981002760435</v>
       </c>
-      <c r="D28" s="0">
+      <c r="D28">
         <v>8.3414083002536188</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="0">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29">
         <v>0.15912559623440875</v>
       </c>
-      <c r="B29" s="0">
+      <c r="B29">
         <v>0.52316910281015983</v>
       </c>
-      <c r="C29" s="0">
+      <c r="C29">
         <v>5.0872403468337186</v>
       </c>
-      <c r="D29" s="0">
+      <c r="D29">
         <v>8.4281147505993097</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="0">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30">
         <v>0.14180876860257302</v>
       </c>
-      <c r="B30" s="0">
+      <c r="B30">
         <v>0.47994476522216906</v>
       </c>
-      <c r="C30" s="0">
+      <c r="C30">
         <v>5.1489967280277087</v>
       </c>
-      <c r="D30" s="0">
+      <c r="D30">
         <v>8.5071879594251367</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="0">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31">
         <v>0.12639513917563425</v>
       </c>
-      <c r="B31" s="0">
+      <c r="B31">
         <v>0.4397870762012972</v>
       </c>
-      <c r="C31" s="0">
+      <c r="C31">
         <v>5.2056497046809183</v>
       </c>
-      <c r="D31" s="0">
+      <c r="D31">
         <v>8.5792545655052841</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="0">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32">
         <v>0.11267095683500016</v>
       </c>
-      <c r="B32" s="0">
+      <c r="B32">
         <v>0.40256204497584713</v>
       </c>
-      <c r="C32" s="0">
+      <c r="C32">
         <v>5.257562018762135</v>
       </c>
-      <c r="D32" s="0">
+      <c r="D32">
         <v>8.6448910619271349</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="0">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33">
         <v>0.10043579977916164</v>
       </c>
-      <c r="B33" s="0">
+      <c r="B33">
         <v>0.36815823243609358</v>
       </c>
-      <c r="C33" s="0">
+      <c r="C33">
         <v>5.305059595870417</v>
       </c>
-      <c r="D33" s="0">
+      <c r="D33">
         <v>8.7046237960912567</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="0">
-        <v>0.089508750637186455</v>
-      </c>
-      <c r="B34" s="0">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>8.9508750637186454E-2</v>
+      </c>
+      <c r="B34">
         <v>0.33646151466324886</v>
       </c>
-      <c r="C34" s="0">
+      <c r="C34">
         <v>5.348450173251341</v>
       </c>
-      <c r="D34" s="0">
+      <c r="D34">
         <v>8.7589414226141553</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="0">
-        <v>0.079758987429950925</v>
-      </c>
-      <c r="B35" s="0">
-        <v>0.3072645190880885</v>
-      </c>
-      <c r="C35" s="0">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>7.9758987429950925E-2</v>
+      </c>
+      <c r="B35">
+        <v>0.30726451908808849</v>
+      </c>
+      <c r="C35">
         <v>5.3880811259430166</v>
       </c>
-      <c r="D35" s="0">
+      <c r="D35">
         <v>8.8083221385130663</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="0">
-        <v>0.071072377669143927</v>
-      </c>
-      <c r="B36" s="0">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>7.1072377669143927E-2</v>
+      </c>
+      <c r="B36">
         <v>0.28038385270575644</v>
       </c>
-      <c r="C36" s="0">
+      <c r="C36">
         <v>5.4242579887360369</v>
       </c>
-      <c r="D36" s="0">
+      <c r="D36">
         <v>8.8531856110668929</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="0">
-        <v>0.063340066706460668</v>
-      </c>
-      <c r="B37" s="0">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>6.3340066706460668E-2</v>
+      </c>
+      <c r="B37">
         <v>0.25565532344641684</v>
       </c>
-      <c r="C37" s="0">
+      <c r="C37">
         <v>5.4572614472712306</v>
       </c>
-      <c r="D37" s="0">
+      <c r="D37">
         <v>8.8939213805647697</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="0">
-        <v>0.056458942441372943</v>
-      </c>
-      <c r="B38" s="0">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>5.6458942441372943E-2</v>
+      </c>
+      <c r="B38">
         <v>0.23293043414874534</v>
       </c>
-      <c r="C38" s="0">
+      <c r="C38">
         <v>5.4873503467473288</v>
       </c>
-      <c r="D38" s="0">
+      <c r="D38">
         <v>8.9308914043059566</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="0">
-        <v>0.050331635321129421</v>
-      </c>
-      <c r="B39" s="0">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>5.0331635321129421E-2</v>
+      </c>
+      <c r="B39">
         <v>0.21207638255993005</v>
       </c>
-      <c r="C39" s="0">
+      <c r="C39">
         <v>5.5147616919209659</v>
       </c>
-      <c r="D39" s="0">
+      <c r="D39">
         <v>8.9644300565998378</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="0">
-        <v>0.044866518340755376</v>
-      </c>
-      <c r="B40" s="0">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>4.4866518340755376E-2</v>
+      </c>
+      <c r="B40">
         <v>0.19297606133567044</v>
       </c>
-      <c r="C40" s="0">
+      <c r="C40">
         <v>5.5397106471066788</v>
       </c>
-      <c r="D40" s="0">
+      <c r="D40">
         <v>8.9948441287659247</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="0">
-        <v>0.039983801510337098</v>
-      </c>
-      <c r="B41" s="0">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>3.9983801510337098E-2</v>
+      </c>
+      <c r="B41">
         <v>0.17551112430144522</v>
       </c>
-      <c r="C41" s="0">
+      <c r="C41">
         <v>5.5624009477664398</v>
       </c>
-      <c r="D41" s="0">
+      <c r="D41">
         <v>9.0224171462561031</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="0">
-        <v>0.035628366724398737</v>
-      </c>
-      <c r="B42" s="0">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>3.5628366724398737E-2</v>
+      </c>
+      <c r="B42">
         <v>0.15954012322760702</v>
       </c>
-      <c r="C42" s="0">
+      <c r="C42">
         <v>5.5830330281725979</v>
       </c>
-      <c r="D42" s="0">
-        <v>9.0474046614481996</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="0">
-        <v>0.031748573317004723</v>
-      </c>
-      <c r="B43" s="0">
+      <c r="D42">
+        <v>9.0474046614481995</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>3.1748573317004723E-2</v>
+      </c>
+      <c r="B43">
         <v>0.14494391536341777</v>
       </c>
-      <c r="C43" s="0">
+      <c r="C43">
         <v>5.6017812956482089</v>
       </c>
-      <c r="D43" s="0">
+      <c r="D43">
         <v>9.0700327223312041</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="0">
-        <v>0.028295286949747166</v>
-      </c>
-      <c r="B44" s="0">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>2.8295286949747166E-2</v>
+      </c>
+      <c r="B44">
         <v>0.13161272071385227</v>
       </c>
-      <c r="C44" s="0">
+      <c r="C44">
         <v>5.618808112550453</v>
       </c>
-      <c r="D44" s="0">
+      <c r="D44">
         <v>9.0905128256007064</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="0">
-        <v>0.025221998413256067</v>
-      </c>
-      <c r="B45" s="0">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>2.5221998413256067E-2</v>
+      </c>
+      <c r="B45">
         <v>0.11944564521000099</v>
       </c>
-      <c r="C45" s="0">
+      <c r="C45">
         <v>5.6342641459617777</v>
       </c>
-      <c r="D45" s="0">
+      <c r="D45">
         <v>9.1090421475485215</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="0">
-        <v>0.022484823627199221</v>
-      </c>
-      <c r="B46" s="0">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>2.2484823627199221E-2</v>
+      </c>
+      <c r="B46">
         <v>0.10835068070906977</v>
       </c>
-      <c r="C46" s="0">
+      <c r="C46">
         <v>5.6482883676898918</v>
       </c>
-      <c r="D46" s="0">
+      <c r="D46">
         <v>9.125803544062693</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="0">
-        <v>0.020042503741145711</v>
-      </c>
-      <c r="B47" s="0">
-        <v>0.09824470472762005</v>
-      </c>
-      <c r="C47" s="0">
-        <v>5.661008054426592</v>
-      </c>
-      <c r="D47" s="0">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>2.004250374114571E-2</v>
+      </c>
+      <c r="B47">
+        <v>9.824470472762005E-2</v>
+      </c>
+      <c r="C47">
+        <v>5.6610080544265919</v>
+      </c>
+      <c r="D47">
         <v>9.140965550685447</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="0">
-        <v>0.017860718766393356</v>
-      </c>
-      <c r="B48" s="0">
-        <v>0.089045985065136057</v>
-      </c>
-      <c r="C48" s="0">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>1.7860718766393356E-2</v>
+      </c>
+      <c r="B48">
+        <v>8.9045985065136057E-2</v>
+      </c>
+      <c r="C48">
         <v>5.6725416667813544</v>
       </c>
-      <c r="D48" s="0">
+      <c r="D48">
         <v>9.1546809480149633</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="0">
-        <v>0.015915098999078357</v>
-      </c>
-      <c r="B49" s="0">
-        <v>0.080675112226063078</v>
-      </c>
-      <c r="C49" s="0">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>1.5915098999078357E-2</v>
+      </c>
+      <c r="B49">
+        <v>8.0675112226063078E-2</v>
+      </c>
+      <c r="C49">
         <v>5.6829946941082561</v>
       </c>
-      <c r="D49" s="0">
+      <c r="D49">
         <v>9.167079595109179</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="0">
-        <v>0.014182267603828194</v>
-      </c>
-      <c r="B50" s="0">
-        <v>0.073062478817479334</v>
-      </c>
-      <c r="C50" s="0">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>1.4182267603828194E-2</v>
+      </c>
+      <c r="B50">
+        <v>7.3062478817479334E-2</v>
+      </c>
+      <c r="C50">
         <v>5.6924617611152657</v>
       </c>
-      <c r="D50" s="0">
+      <c r="D50">
         <v>9.1782794935114378</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="0">
-        <v>0.012640043503892081</v>
-      </c>
-      <c r="B51" s="0">
-        <v>0.066143286117278752</v>
-      </c>
-      <c r="C51" s="0">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>1.2640043503892081E-2</v>
+      </c>
+      <c r="B51">
+        <v>6.6143286117278752E-2</v>
+      </c>
+      <c r="C51">
         <v>5.7010314041680292</v>
       </c>
-      <c r="D51" s="0">
+      <c r="D51">
         <v>9.1883913606641379</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="0">
-        <v>0.011267441381140905</v>
-      </c>
-      <c r="B52" s="0">
-        <v>0.059857544074170974</v>
-      </c>
-      <c r="C52" s="0">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>1.1267441381140905E-2</v>
+      </c>
+      <c r="B52">
+        <v>5.9857544074170974E-2</v>
+      </c>
+      <c r="C52">
         <v>5.7087860712898708</v>
       </c>
-      <c r="D52" s="0">
+      <c r="D52">
         <v>9.1975186299087319</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="0">
-        <v>0.010044671676067256</v>
-      </c>
-      <c r="B53" s="0">
-        <v>0.054150071307681291</v>
-      </c>
-      <c r="C53" s="0">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>1.0044671676067256E-2</v>
+      </c>
+      <c r="B53">
+        <v>5.4150071307681291E-2</v>
+      </c>
+      <c r="C53">
         <v>5.7158021221617901</v>
       </c>
-      <c r="D53" s="0">
+      <c r="D53">
         <v>9.2057574504857236</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="0">
-        <v>0.0089531784705908606</v>
-      </c>
-      <c r="B54" s="0">
-        <v>0.048970440872528012</v>
-      </c>
-      <c r="C54" s="0">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>8.9531784705908606E-3</v>
+      </c>
+      <c r="B54">
+        <v>4.8970440872528012E-2</v>
+      </c>
+      <c r="C54">
         <v>5.7221498418168393</v>
       </c>
-      <c r="D54" s="0">
+      <c r="D54">
         <v>9.2131966633462508</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="0">
-        <v>0.0079783463501675277</v>
-      </c>
-      <c r="B55" s="0">
-        <v>0.044271034080099726</v>
-      </c>
-      <c r="C55" s="0">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>7.9783463501675277E-3</v>
+      </c>
+      <c r="B55">
+        <v>4.4271034080099726E-2</v>
+      </c>
+      <c r="C55">
         <v>5.7278924900012989</v>
       </c>
-      <c r="D55" s="0">
+      <c r="D55">
         <v>9.2199141436511329</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="0">
-        <v>0.007109249879023569</v>
-      </c>
-      <c r="B56" s="0">
-        <v>0.040009674316081816</v>
-      </c>
-      <c r="C56" s="0">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>7.109249879023569E-3</v>
+      </c>
+      <c r="B56">
+        <v>4.0009674316081816E-2</v>
+      </c>
+      <c r="C56">
         <v>5.7330839354625063</v>
       </c>
-      <c r="D56" s="0">
+      <c r="D56">
         <v>9.2259746855834841</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="0">
-        <v>0.0063353319005524031</v>
-      </c>
-      <c r="B57" s="0">
-        <v>0.036148078884712408</v>
-      </c>
-      <c r="C57" s="0">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>6.3353319005524031E-3</v>
+      </c>
+      <c r="B57">
+        <v>3.6148078884712408E-2</v>
+      </c>
+      <c r="C57">
         <v>5.7377737589059237</v>
       </c>
-      <c r="D57" s="0">
+      <c r="D57">
         <v>9.231438427005374</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="0">
-        <v>0.005646580041200059</v>
-      </c>
-      <c r="B58" s="0">
-        <v>0.032650483514482957</v>
-      </c>
-      <c r="C58" s="0">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>5.646580041200059E-3</v>
+      </c>
+      <c r="B58">
+        <v>3.2650483514482957E-2</v>
+      </c>
+      <c r="C58">
         <v>5.7420084395993198</v>
       </c>
-      <c r="D58" s="0">
+      <c r="D58">
         <v>9.2363618595581212</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="0">
-        <v>0.005033526710465243</v>
-      </c>
-      <c r="B59" s="0">
-        <v>0.029483642358138554</v>
-      </c>
-      <c r="C59" s="0">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>5.033526710465243E-3</v>
+      </c>
+      <c r="B59">
+        <v>2.9483642358138554E-2</v>
+      </c>
+      <c r="C59">
         <v>5.7458313553727667</v>
       </c>
-      <c r="D59" s="0">
+      <c r="D59">
         <v>9.240797828662302</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="0">
-        <v>0.0044872491008992798</v>
-      </c>
-      <c r="B60" s="0">
-        <v>0.026616827992677689</v>
-      </c>
-      <c r="C60" s="0">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>4.4872491008992798E-3</v>
+      </c>
+      <c r="B60">
+        <v>2.6616827992677689E-2</v>
+      </c>
+      <c r="C60">
         <v>5.7492827826186401</v>
       </c>
-      <c r="D60" s="0">
+      <c r="D60">
         <v>9.2447955335177419</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="0">
-        <v>0.0039994442800411973</v>
-      </c>
-      <c r="B61" s="0">
-        <v>0.024021804451712554</v>
-      </c>
-      <c r="C61" s="0">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>3.9994442800411973E-3</v>
+      </c>
+      <c r="B61">
+        <v>2.4021804451712554E-2</v>
+      </c>
+      <c r="C61">
         <v>5.7523998428977166</v>
       </c>
-      <c r="D61" s="0">
+      <c r="D61">
         <v>9.2484003986176759</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="0">
-        <v>0.0035639051711658489</v>
-      </c>
-      <c r="B62" s="0">
-        <v>0.021673221866462641</v>
-      </c>
-      <c r="C62" s="0">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>3.5639051711658489E-3</v>
+      </c>
+      <c r="B62">
+        <v>2.1673221866462641E-2</v>
+      </c>
+      <c r="C62">
         <v>5.7552145287398329</v>
       </c>
-      <c r="D62" s="0">
+      <c r="D62">
         <v>9.2516506235686684</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="0">
-        <v>0.0031756985569088561</v>
-      </c>
-      <c r="B63" s="0">
-        <v>0.01954928343569581</v>
-      </c>
-      <c r="C63" s="0">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>3.1756985569088561E-3</v>
+      </c>
+      <c r="B63">
+        <v>1.954928343569581E-2</v>
+      </c>
+      <c r="C63">
         <v>5.7577539163542788</v>
       </c>
-      <c r="D63" s="0">
+      <c r="D63">
         <v>9.2545782177973699</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="0">
-        <v>0.0028300571146443972</v>
-      </c>
-      <c r="B64" s="0">
-        <v>0.017629773704703051</v>
-      </c>
-      <c r="C64" s="0">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>2.8300571146443972E-3</v>
+      </c>
+      <c r="B64">
+        <v>1.7629773704703051E-2</v>
+      </c>
+      <c r="C64">
         <v>5.760043323067344</v>
       </c>
-      <c r="D64" s="0">
+      <c r="D64">
         <v>9.2572132659527</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="0">
-        <v>0.0025224617200111468</v>
-      </c>
-      <c r="B65" s="0">
-        <v>0.015895765866769201</v>
-      </c>
-      <c r="C65" s="0">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>2.5224617200111468E-3</v>
+      </c>
+      <c r="B65">
+        <v>1.5895765866769201E-2</v>
+      </c>
+      <c r="C65">
         <v>5.7621065119416395</v>
       </c>
-      <c r="D65" s="0">
+      <c r="D65">
         <v>9.2595840502216298</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="0">
-        <v>0.002248641446912311</v>
-      </c>
-      <c r="B66" s="0">
-        <v>0.014329621763173133</v>
-      </c>
-      <c r="C66" s="0">
-        <v>5.7639656917760958</v>
-      </c>
-      <c r="D66" s="0">
-        <v>9.2617170503291853</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="0">
-        <v>0.0020045735675155996</v>
-      </c>
-      <c r="B67" s="0">
-        <v>0.012914991883187609</v>
-      </c>
-      <c r="C67" s="0">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>2.248641446912311E-3</v>
+      </c>
+      <c r="B66">
+        <v>1.4329621763173133E-2</v>
+      </c>
+      <c r="C66">
+        <v>5.7639656917760957</v>
+      </c>
+      <c r="D66">
+        <v>9.2617170503291852</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>2.0045735675155996E-3</v>
+      </c>
+      <c r="B67">
+        <v>1.2914991883187609E-2</v>
+      </c>
+      <c r="C67">
         <v>5.7656415171059621</v>
       </c>
-      <c r="D67" s="0">
+      <c r="D67">
         <v>9.2636369435384474</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="0">
-        <v>0.0017865681742323268</v>
-      </c>
-      <c r="B68" s="0">
-        <v>0.011636866751639233</v>
-      </c>
-      <c r="C68" s="0">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>1.7865681742323268E-3</v>
+      </c>
+      <c r="B68">
+        <v>1.1636866751639233E-2</v>
+      </c>
+      <c r="C68">
         <v>5.7671529462548836</v>
       </c>
-      <c r="D68" s="0">
+      <c r="D68">
         <v>9.2653663780806532</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="0">
-        <v>0.0015919852516569531</v>
-      </c>
-      <c r="B69" s="0">
-        <v>0.010482445418357748</v>
-      </c>
-      <c r="C69" s="0">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <v>1.5919852516569531E-3</v>
+      </c>
+      <c r="B69">
+        <v>1.0482445418357748E-2</v>
+      </c>
+      <c r="C69">
         <v>5.7685156054526754</v>
       </c>
-      <c r="D69" s="0">
+      <c r="D69">
         <v>9.2669236202010197</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="0">
-        <v>0.0014185873238042727</v>
-      </c>
-      <c r="B70" s="0">
-        <v>0.0094406629461032746</v>
-      </c>
-      <c r="C70" s="0">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <v>1.4185873238042727E-3</v>
+      </c>
+      <c r="B70">
+        <v>9.4406629461032746E-3</v>
+      </c>
+      <c r="C70">
         <v>5.7697429541284215</v>
       </c>
-      <c r="D70" s="0">
+      <c r="D70">
         <v>9.2683243668046185</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="0">
-        <v>0.0012642217689610626</v>
-      </c>
-      <c r="B71" s="0">
-        <v>0.0085011393490703659</v>
-      </c>
-      <c r="C71" s="0">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <v>1.2642217689610626E-3</v>
+      </c>
+      <c r="B71">
+        <v>8.5011393490703659E-3</v>
+      </c>
+      <c r="C71">
         <v>5.7708476759508125</v>
       </c>
-      <c r="D71" s="0">
+      <c r="D71">
         <v>9.2695834541818538</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="0">
-        <v>0.0011268490423857734</v>
-      </c>
-      <c r="B72" s="0">
-        <v>0.0076541426548690193</v>
-      </c>
-      <c r="C72" s="0">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <v>1.1268490423857734E-3</v>
+      </c>
+      <c r="B72">
+        <v>7.6541426548690193E-3</v>
+      </c>
+      <c r="C72">
         <v>5.7718416855629284</v>
       </c>
-      <c r="D72" s="0">
+      <c r="D72">
         <v>9.2707148365205434</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="0">
-        <v>0.0010045426763085367</v>
-      </c>
-      <c r="B73" s="0">
-        <v>0.0068905889045247264</v>
-      </c>
-      <c r="C73" s="0">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <v>1.0045426763085367E-3</v>
+      </c>
+      <c r="B73">
+        <v>6.8905889045247264E-3</v>
+      </c>
+      <c r="C73">
         <v>5.7727361285822321</v>
       </c>
-      <c r="D73" s="0">
+      <c r="D73">
         <v>9.2717315859059255</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="0">
-        <v>0.00089548927993116675</v>
-      </c>
-      <c r="B74" s="0">
-        <v>0.0062020421524784843</v>
-      </c>
-      <c r="C74" s="0">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <v>8.9548927993116675E-4</v>
+      </c>
+      <c r="B74">
+        <v>6.2020421524784843E-3</v>
+      </c>
+      <c r="C74">
         <v>5.7735413816005767</v>
       </c>
-      <c r="D74" s="0">
+      <c r="D74">
         <v>9.2726458923206483</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="0">
-        <v>0.00079806350547478768</v>
-      </c>
-      <c r="B75" s="0">
-        <v>0.0055808260517159342</v>
-      </c>
-      <c r="C75" s="0">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <v>7.9806350547478768E-4</v>
+      </c>
+      <c r="B75">
+        <v>5.5808260517159342E-3</v>
+      </c>
+      <c r="C75">
         <v>5.7742668603722489</v>
       </c>
-      <c r="D75" s="0">
+      <c r="D75">
         <v>9.2734687968667764</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="0">
-        <v>0.00071113476355270477</v>
-      </c>
-      <c r="B76" s="0">
-        <v>0.0050206791909165553</v>
-      </c>
-      <c r="C76" s="0">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <v>7.1113476355270477E-4</v>
+      </c>
+      <c r="B76">
+        <v>5.0206791909165552E-3</v>
+      </c>
+      <c r="C76">
         <v>5.7749200362375612</v>
       </c>
-      <c r="D76" s="0">
+      <c r="D76">
         <v>9.2742089014740117</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="0">
-        <v>0.00063368643044673181</v>
-      </c>
-      <c r="B77" s="0">
-        <v>0.0045160598113449836</v>
-      </c>
-      <c r="C77" s="0">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <v>6.3368643044673181E-4</v>
+      </c>
+      <c r="B77">
+        <v>4.5160598113449836E-3</v>
+      </c>
+      <c r="C77">
         <v>5.7755075389209836</v>
       </c>
-      <c r="D77" s="0">
+      <c r="D77">
         <v>9.2748738524905399</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="0">
-        <v>0.00056474659655419144</v>
-      </c>
-      <c r="B78" s="0">
-        <v>0.004061746072926033</v>
-      </c>
-      <c r="C78" s="0">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <v>5.6474659655419144E-4</v>
+      </c>
+      <c r="B78">
+        <v>4.061746072926033E-3</v>
+      </c>
+      <c r="C78">
         <v>5.7760356303763745</v>
       </c>
-      <c r="D78" s="0">
+      <c r="D78">
         <v>9.275470883779823</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="0">
-        <v>0.00050339486915585417</v>
-      </c>
-      <c r="B79" s="0">
-        <v>0.0036528376314416229</v>
-      </c>
-      <c r="C79" s="0">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <v>5.0339486915585417E-4</v>
+      </c>
+      <c r="B79">
+        <v>3.6528376314416229E-3</v>
+      </c>
+      <c r="C79">
         <v>5.7765101959296361</v>
       </c>
-      <c r="D79" s="0">
+      <c r="D79">
         <v>9.2760068010604826</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="0">
-        <v>0.00044876237241593301</v>
-      </c>
-      <c r="B80" s="0">
-        <v>0.0032847556385307412</v>
-      </c>
-      <c r="C80" s="0">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <v>4.4876237241593301E-4</v>
+      </c>
+      <c r="B80">
+        <v>3.2847556385307412E-3</v>
+      </c>
+      <c r="C80">
         <v>5.7769367442787072</v>
       </c>
-      <c r="D80" s="0">
+      <c r="D80">
         <v>9.2764879819062944</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="0">
-        <v>0.00040003174738208853</v>
-      </c>
-      <c r="B81" s="0">
-        <v>0.0029532427416894772</v>
-      </c>
-      <c r="C81" s="0">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <v>4.0003174738208853E-4</v>
+      </c>
+      <c r="B81">
+        <v>2.9532427416894772E-3</v>
+      </c>
+      <c r="C81">
         <v>5.7773204074935673</v>
       </c>
-      <c r="D81" s="0">
-        <v>9.2769203757461885</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="0">
-        <v>0.00035649192636826932</v>
-      </c>
-      <c r="B82" s="0">
-        <v>0.0026544842960053187</v>
-      </c>
-      <c r="C82" s="0">
+      <c r="D81">
+        <v>9.2769203757461884</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <v>3.5649192636826932E-4</v>
+      </c>
+      <c r="B82">
+        <v>2.6544842960053187E-3</v>
+      </c>
+      <c r="C82">
         <v>5.7776657611863014</v>
       </c>
-      <c r="D82" s="0">
+      <c r="D82">
         <v>9.2773092692599359</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="0">
-        <v>0.00031765070050228649</v>
-      </c>
-      <c r="B83" s="0">
-        <v>0.002385463908884832</v>
-      </c>
-      <c r="C83" s="0">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <v>3.1765070050228649E-4</v>
+      </c>
+      <c r="B83">
+        <v>2.385463908884832E-3</v>
+      </c>
+      <c r="C83">
         <v>5.7779763484993492</v>
       </c>
-      <c r="D83" s="0">
+      <c r="D83">
         <v>9.2776586977988487</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="0">
-        <v>0.00028305191052003327</v>
-      </c>
-      <c r="B84" s="0">
-        <v>0.0021434585850556398</v>
-      </c>
-      <c r="C84" s="0">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <v>2.8305191052003327E-4</v>
+      </c>
+      <c r="B84">
+        <v>2.1434585850556398E-3</v>
+      </c>
+      <c r="C84">
         <v>5.7782553805984218</v>
       </c>
-      <c r="D84" s="0">
+      <c r="D84">
         <v>9.2779723286879037</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="0">
-        <v>0.00025226052526960985</v>
-      </c>
-      <c r="B85" s="0">
-        <v>0.0019258959941812421</v>
-      </c>
-      <c r="C85" s="0">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <v>2.5226052526960985E-4</v>
+      </c>
+      <c r="B85">
+        <v>1.9258959941812421E-3</v>
+      </c>
+      <c r="C85">
         <v>5.7785058953735122</v>
       </c>
-      <c r="D85" s="0">
+      <c r="D85">
         <v>9.2782536348482445</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="0">
-        <v>0.0002248632893520381</v>
-      </c>
-      <c r="B86" s="0">
-        <v>0.001730355145449483</v>
-      </c>
-      <c r="C86" s="0">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <v>2.248632893520381E-4</v>
+      </c>
+      <c r="B86">
+        <v>1.730355145449483E-3</v>
+      </c>
+      <c r="C86">
         <v>5.7787307560712078</v>
       </c>
-      <c r="D86" s="0">
+      <c r="D86">
         <v>9.2785058927818582</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="0">
-        <v>0.0002004687231212593</v>
-      </c>
-      <c r="B87" s="0">
-        <v>0.0015545663875725316</v>
-      </c>
-      <c r="C87" s="0">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <v>2.004687231212593E-4</v>
+      </c>
+      <c r="B87">
+        <v>1.5545663875725316E-3</v>
+      </c>
+      <c r="C87">
         <v>5.7789326512947001</v>
       </c>
-      <c r="D87" s="0">
+      <c r="D87">
         <v>9.2787321825715807</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="0">
-        <v>0.0001787071226841366</v>
-      </c>
-      <c r="B88" s="0">
-        <v>0.0013964114087869032</v>
-      </c>
-      <c r="C88" s="0">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <v>1.7870712268413659E-4</v>
+      </c>
+      <c r="B88">
+        <v>1.3964114087869032E-3</v>
+      </c>
+      <c r="C88">
         <v>5.779114095003778</v>
       </c>
-      <c r="D88" s="0">
+      <c r="D88">
         <v>9.2789353878810967</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="0">
-        <v>0.00015925250658644109</v>
-      </c>
-      <c r="B89" s="0">
-        <v>0.0012539811927962004</v>
-      </c>
-      <c r="C89" s="0">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <v>1.5925250658644109E-4</v>
+      </c>
+      <c r="B89">
+        <v>1.2539811927962004E-3</v>
+      </c>
+      <c r="C89">
         <v>5.7792773450720842</v>
       </c>
-      <c r="D89" s="0">
+      <c r="D89">
         <v>9.2791180925655006</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="0">
-        <v>0.0001418864569251608</v>
-      </c>
-      <c r="B90" s="0">
-        <v>0.0011258173862492842</v>
-      </c>
-      <c r="C90" s="0">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <v>1.418864569251608E-4</v>
+      </c>
+      <c r="B90">
+        <v>1.1258173862492842E-3</v>
+      </c>
+      <c r="C90">
         <v>5.7794240935984442</v>
       </c>
-      <c r="D90" s="0">
+      <c r="D90">
         <v>9.279282207141522</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="0">
-        <v>0.00012641494732308097</v>
-      </c>
-      <c r="B91" s="0">
-        <v>0.0010106420096158716</v>
-      </c>
-      <c r="C91" s="0">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <v>1.2641494732308097E-4</v>
+      </c>
+      <c r="B91">
+        <v>1.0106420096158716E-3</v>
+      </c>
+      <c r="C91">
         <v>5.7795558262046516</v>
       </c>
-      <c r="D91" s="0">
+      <c r="D91">
         <v>9.2794294112573308</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="0">
-        <v>0.00011265071655757604</v>
-      </c>
-      <c r="B92" s="0">
-        <v>0.00090723726900283366</v>
-      </c>
-      <c r="C92" s="0">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <v>1.1265071655757604E-4</v>
+      </c>
+      <c r="B92">
+        <v>9.0723726900283365E-4</v>
+      </c>
+      <c r="C92">
         <v>5.779673961086961</v>
       </c>
-      <c r="D92" s="0">
+      <c r="D92">
         <v>9.279561310370406</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="0">
-        <v>0.00010041357769347932</v>
-      </c>
-      <c r="B93" s="0">
-        <v>0.00081444561697486249</v>
-      </c>
-      <c r="C93" s="0">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <v>1.0041357769347932E-4</v>
+      </c>
+      <c r="B93">
+        <v>8.1444561697486249E-4</v>
+      </c>
+      <c r="C93">
         <v>5.7797798486244396</v>
       </c>
-      <c r="D93" s="0">
+      <c r="D93">
         <v>9.2796794350467486</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="0">
-        <v>8.953041808308133e-05</v>
-      </c>
-      <c r="B94" s="0">
-        <v>0.00073116975255445999</v>
-      </c>
-      <c r="C94" s="0">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <v>8.953041808308133E-5</v>
+      </c>
+      <c r="B94">
+        <v>7.3116975255445998E-4</v>
+      </c>
+      <c r="C94">
         <v>5.77987477137897</v>
       </c>
-      <c r="D94" s="0">
+      <c r="D94">
         <v>9.279785240960889</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="0">
-        <v>7.9835199366131375e-05</v>
-      </c>
-      <c r="B95" s="0">
-        <v>0.00065637262122194922</v>
-      </c>
-      <c r="C95" s="0">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <v>7.9835199366131375E-5</v>
+      </c>
+      <c r="B95">
+        <v>6.5637262122194922E-4</v>
+      </c>
+      <c r="C95">
         <v>5.7799599440952445</v>
       </c>
-      <c r="D95" s="0">
+      <c r="D95">
         <v>9.2798801088958811</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="0">
-        <v>7.1169387675383504e-05</v>
-      </c>
-      <c r="B96" s="0">
-        <v>0.00058907915060226639</v>
-      </c>
-      <c r="C96" s="0">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A96">
+        <v>7.1169387675383504E-5</v>
+      </c>
+      <c r="B96">
+        <v>5.8907915060226639E-4</v>
+      </c>
+      <c r="C96">
         <v>5.7800365115046919</v>
       </c>
-      <c r="D96" s="0">
+      <c r="D96">
         <v>9.2799653421170181</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="0">
-        <v>6.3427414795821674e-05</v>
-      </c>
-      <c r="B97" s="0">
-        <v>0.00052856020886020406</v>
-      </c>
-      <c r="C97" s="0">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <v>6.3427414795821674E-5</v>
+      </c>
+      <c r="B97">
+        <v>5.2856020886020406E-4</v>
+      </c>
+      <c r="C97">
         <v>5.7801053157156552</v>
       </c>
-      <c r="D97" s="0">
+      <c r="D97">
         <v>9.2800418883008611</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="0">
-        <v>5.6528050324323279e-05</v>
-      </c>
-      <c r="B98" s="0">
-        <v>0.00047421388992528968</v>
-      </c>
-      <c r="C98" s="0">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <v>5.6528050324323279E-5</v>
+      </c>
+      <c r="B98">
+        <v>4.7421388992528968E-4</v>
+      </c>
+      <c r="C98">
         <v>5.7801670455649896</v>
       </c>
-      <c r="D98" s="0">
+      <c r="D98">
         <v>9.2801105175146681</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="0">
-        <v>5.0380285472993472e-05</v>
-      </c>
-      <c r="B99" s="0">
-        <v>0.00042541989310455788</v>
-      </c>
-      <c r="C99" s="0">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <v>5.0380285472993472E-5</v>
+      </c>
+      <c r="B99">
+        <v>4.2541989310455788E-4</v>
+      </c>
+      <c r="C99">
         <v>5.7802224187487568</v>
       </c>
-      <c r="D99" s="0">
+      <c r="D99">
         <v>9.2801720384632862</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="0">
-        <v>4.4901164755635793e-05</v>
-      </c>
-      <c r="B100" s="0">
-        <v>0.00038161036925499453</v>
-      </c>
-      <c r="C100" s="0">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <v>4.4901164755635793E-5</v>
+      </c>
+      <c r="B100">
+        <v>3.8161036925499453E-4</v>
+      </c>
+      <c r="C100">
         <v>5.780272091893023</v>
       </c>
-      <c r="D100" s="0">
+      <c r="D100">
         <v>9.2802271907282687</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A100"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" customWidth="true"/>
+    <col min="1" max="1" width="13.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1">
         <v>0</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>0.020202020202020204</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>2.0202020202020204E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>0.040404040404040408</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>4.0404040404040407E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>0.060606060606060608</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>6.0606060606060608E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>0.080808080808080815</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>8.0808080808080815E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>0.10101010101010101</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>0.12121212121212122</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>0.14141414141414141</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>0.16161616161616163</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>0.18181818181818182</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>0.20202020202020202</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>0.22222222222222221</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>0.24242424242424243</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>0.26262626262626265</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>0.28282828282828282</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>0.30303030303030304</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>0.32323232323232326</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>0.34343434343434343</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>0.36363636363636365</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>0.38383838383838381</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>0.40404040404040403</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>0.42424242424242426</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>0.42424242424242425</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>0.44444444444444442</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>0.46464646464646464</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>0.48484848484848486</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>0.50505050505050508</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>0.52525252525252531</v>
-      </c>
-    </row>
-    <row r="28">
+        <v>0.5252525252525253</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>0.54545454545454541</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>0.56565656565656564</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>0.58585858585858586</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>0.60606060606060608</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>0.6262626262626263</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>0.64646464646464652</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>0.68686868686868685</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>0.70707070707070707</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>0.72727272727272729</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>0.74747474747474751</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>0.76767676767676762</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>0.78787878787878785</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>0.80808080808080807</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>0.82828282828282829</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>0.84848484848484851</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>0.86868686868686873</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>0.88888888888888884</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>0.90909090909090906</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>0.92929292929292928</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>0.9494949494949495</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>0.96969696969696972</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>0.98989898989898995</v>
-      </c>
-    </row>
-    <row r="51">
+        <v>0.98989898989898994</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>1.0101010101010102</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>1.0303030303030303</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>1.0505050505050506</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>1.0707070707070707</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>1.0909090909090908</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>1.1111111111111112</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>1.1313131313131313</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>1.1515151515151516</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>1.1717171717171717</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>1.1919191919191918</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>1.2121212121212122</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>1.2323232323232323</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>1.2525252525252526</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>1.2727272727272727</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>1.292929292929293</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>1.3131313131313131</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>1.3333333333333333</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>1.3535353535353536</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>1.3737373737373737</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>1.393939393939394</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>1.4141414141414141</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>1.4343434343434343</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>1.4545454545454546</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>1.4747474747474747</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>1.494949494949495</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>1.5151515151515151</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A77">
-        <v>1.5353535353535353</v>
-      </c>
-    </row>
-    <row r="78">
+        <v>1.5353535353535352</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>1.5555555555555556</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>1.5757575757575757</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>1.595959595959596</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>1.6161616161616161</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>1.6363636363636365</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>1.6565656565656566</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>1.6767676767676767</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>1.696969696969697</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>1.7171717171717171</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>1.7373737373737375</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>1.7575757575757576</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>1.7777777777777777</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>1.797979797979798</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>1.8181818181818181</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>1.8383838383838385</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>1.8585858585858586</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>1.8787878787878789</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>1.898989898989899</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>1.9191919191919191</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A97">
-        <v>1.9393939393939395</v>
-      </c>
-    </row>
-    <row r="98">
+        <v>1.9393939393939394</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>1.9595959595959596</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>1.9797979797979799</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>2</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>